--- a/scenarios/Coal_Flexibilisation/sub_scenarios/transmission_expansion.xlsx
+++ b/scenarios/Coal_Flexibilisation/sub_scenarios/transmission_expansion.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Meridian Dropbox\ME Projects\01 PROJECTS &amp; PROPOSALS\PyPSA scenarios\Coal flex\sub_scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agatha.majcher\Downloads\agma0 pypsa-rsa master scenarios-Coal_Flexibilisation\sub_scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74C95E1-BCD8-4B4E-B7B9-4A5391EE54FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995FA7F4-CC78-48C4-BDAA-7A11E2031F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="450" yWindow="-14250" windowWidth="28455" windowHeight="12165" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="transmission_expansion" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -261,10 +261,10 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="4">
+    <cellStyle name="Ausgabe" xfId="3" builtinId="21"/>
     <cellStyle name="Excel Built-in Input" xfId="2" xr:uid="{687A75D4-6262-4264-8B90-233AD72663B2}"/>
     <cellStyle name="Excel Built-in Output" xfId="1" xr:uid="{D101FDCC-76BD-4C53-B3AA-85A46C66F8C3}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Output" xfId="3" builtinId="21"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -585,16 +585,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AT17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AE17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="46" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="31" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>15</v>
       </c>
@@ -611,140 +611,85 @@
         <v>3</v>
       </c>
       <c r="F1" s="2">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="G1" s="2">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="H1" s="2">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="I1" s="2">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="J1" s="2">
-        <v>2024</v>
+        <v>2029</v>
       </c>
       <c r="K1" s="2">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="L1" s="2">
-        <v>2026</v>
+        <v>2031</v>
       </c>
       <c r="M1" s="2">
-        <v>2027</v>
+        <v>2032</v>
       </c>
       <c r="N1" s="2">
-        <v>2028</v>
+        <v>2033</v>
       </c>
       <c r="O1" s="2">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="P1" s="2">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="Q1" s="2">
-        <v>2031</v>
+        <v>2036</v>
       </c>
       <c r="R1" s="2">
-        <v>2032</v>
+        <v>2037</v>
       </c>
       <c r="S1" s="2">
-        <v>2033</v>
+        <v>2038</v>
       </c>
       <c r="T1" s="2">
-        <v>2034</v>
+        <v>2039</v>
       </c>
       <c r="U1" s="2">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="V1" s="2">
-        <v>2036</v>
+        <v>2041</v>
       </c>
       <c r="W1" s="2">
-        <v>2037</v>
+        <v>2042</v>
       </c>
       <c r="X1" s="2">
-        <v>2038</v>
+        <v>2043</v>
       </c>
       <c r="Y1" s="2">
-        <v>2039</v>
+        <v>2044</v>
       </c>
       <c r="Z1" s="2">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="AA1" s="2">
-        <v>2041</v>
+        <v>2046</v>
       </c>
       <c r="AB1" s="2">
-        <v>2042</v>
+        <v>2047</v>
       </c>
       <c r="AC1" s="2">
-        <v>2043</v>
+        <v>2048</v>
       </c>
       <c r="AD1" s="2">
-        <v>2044</v>
+        <v>2049</v>
       </c>
       <c r="AE1" s="2">
-        <v>2045</v>
-      </c>
-      <c r="AF1" s="2">
-        <v>2046</v>
-      </c>
-      <c r="AG1" s="2">
-        <v>2047</v>
-      </c>
-      <c r="AH1" s="2">
-        <v>2048</v>
-      </c>
-      <c r="AI1" s="2">
-        <v>2049</v>
-      </c>
-      <c r="AJ1" s="2">
         <v>2050</v>
       </c>
-      <c r="AK1" s="2">
-        <f t="shared" ref="AK1:AT1" si="0">AJ1+1</f>
-        <v>2051</v>
-      </c>
-      <c r="AL1" s="2">
-        <f t="shared" si="0"/>
-        <v>2052</v>
-      </c>
-      <c r="AM1" s="2">
-        <f t="shared" si="0"/>
-        <v>2053</v>
-      </c>
-      <c r="AN1" s="2">
-        <f t="shared" si="0"/>
-        <v>2054</v>
-      </c>
-      <c r="AO1" s="2">
-        <f t="shared" si="0"/>
-        <v>2055</v>
-      </c>
-      <c r="AP1" s="2">
-        <f t="shared" si="0"/>
-        <v>2056</v>
-      </c>
-      <c r="AQ1" s="2">
-        <f t="shared" si="0"/>
-        <v>2057</v>
-      </c>
-      <c r="AR1" s="2">
-        <f t="shared" si="0"/>
-        <v>2058</v>
-      </c>
-      <c r="AS1" s="2">
-        <f t="shared" si="0"/>
-        <v>2059</v>
-      </c>
-      <c r="AT1" s="2">
-        <f t="shared" si="0"/>
-        <v>2060</v>
-      </c>
     </row>
-    <row r="2" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>4</v>
       </c>
@@ -838,63 +783,8 @@
       <c r="AE2" s="4">
         <v>0</v>
       </c>
-      <c r="AF2" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="4">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="4">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="4">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="1">
-        <f t="shared" ref="AK2:AT2" si="1">AJ2</f>
-        <v>0</v>
-      </c>
-      <c r="AL2" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AM2" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AN2" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AO2" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AP2" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AR2" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AS2" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AT2" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="str">
         <f>A2</f>
         <v>test</v>
@@ -989,63 +879,8 @@
       <c r="AE3" s="1">
         <v>0</v>
       </c>
-      <c r="AF3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="1">
-        <f t="shared" ref="AK3:AT3" si="2">AJ3</f>
-        <v>0</v>
-      </c>
-      <c r="AL3" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AM3" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AN3" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AO3" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AP3" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AR3" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AS3" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AT3" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="str">
         <f>A3</f>
         <v>test</v>
@@ -1140,65 +975,10 @@
       <c r="AE4" s="1">
         <v>0</v>
       </c>
-      <c r="AF4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="1">
-        <f t="shared" ref="AK4:AT4" si="3">AJ4</f>
-        <v>0</v>
-      </c>
-      <c r="AL4" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AM4" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AN4" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AO4" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AP4" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AR4" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AS4" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AT4" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="str">
-        <f t="shared" ref="A5:A17" si="4">A4</f>
+        <f t="shared" ref="A5:A17" si="0">A4</f>
         <v>test</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1291,65 +1071,10 @@
       <c r="AE5" s="1">
         <v>0</v>
       </c>
-      <c r="AF5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="1">
-        <f t="shared" ref="AK5:AT5" si="5">AJ5</f>
-        <v>0</v>
-      </c>
-      <c r="AL5" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AM5" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AN5" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AO5" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AP5" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AR5" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AS5" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AT5" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>test</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1442,65 +1167,10 @@
       <c r="AE6" s="1">
         <v>0</v>
       </c>
-      <c r="AF6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="1">
-        <f t="shared" ref="AK6:AT6" si="6">AJ6</f>
-        <v>0</v>
-      </c>
-      <c r="AL6" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AM6" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AN6" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AO6" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AP6" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AR6" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AS6" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AT6" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>test</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1593,65 +1263,10 @@
       <c r="AE7" s="1">
         <v>0</v>
       </c>
-      <c r="AF7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="1">
-        <f t="shared" ref="AK7:AT7" si="7">AJ7</f>
-        <v>0</v>
-      </c>
-      <c r="AL7" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM7" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AN7" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AO7" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AP7" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AR7" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AS7" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AT7" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>test</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -1744,65 +1359,10 @@
       <c r="AE8" s="1">
         <v>0</v>
       </c>
-      <c r="AF8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="1">
-        <f t="shared" ref="AK8:AT8" si="8">AJ8</f>
-        <v>0</v>
-      </c>
-      <c r="AL8" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AM8" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AN8" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AO8" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AP8" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR8" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AS8" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AT8" s="1">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>test</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1895,65 +1455,10 @@
       <c r="AE9" s="1">
         <v>0</v>
       </c>
-      <c r="AF9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="1">
-        <f t="shared" ref="AK9:AT9" si="9">AJ9</f>
-        <v>0</v>
-      </c>
-      <c r="AL9" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AM9" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AN9" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AO9" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AP9" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AR9" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AS9" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AT9" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>test</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -2046,65 +1551,10 @@
       <c r="AE10" s="1">
         <v>0</v>
       </c>
-      <c r="AF10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="1">
-        <f t="shared" ref="AK10:AT10" si="10">AJ10</f>
-        <v>0</v>
-      </c>
-      <c r="AL10" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AM10" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AN10" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AO10" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AP10" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AR10" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AS10" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AT10" s="1">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="11" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>test</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -2197,65 +1647,10 @@
       <c r="AE11" s="1">
         <v>0</v>
       </c>
-      <c r="AF11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="1">
-        <f t="shared" ref="AK11:AT11" si="11">AJ11</f>
-        <v>0</v>
-      </c>
-      <c r="AL11" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AM11" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN11" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AO11" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AP11" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AR11" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AS11" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AT11" s="1">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="12" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>test</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -2348,65 +1743,10 @@
       <c r="AE12" s="1">
         <v>0</v>
       </c>
-      <c r="AF12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="1">
-        <f t="shared" ref="AK12:AT12" si="12">AJ12</f>
-        <v>0</v>
-      </c>
-      <c r="AL12" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AM12" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AN12" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AO12" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AP12" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AR12" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AS12" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AT12" s="1">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>test</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -2499,65 +1839,10 @@
       <c r="AE13" s="1">
         <v>0</v>
       </c>
-      <c r="AF13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="1">
-        <f t="shared" ref="AK13:AT13" si="13">AJ13</f>
-        <v>0</v>
-      </c>
-      <c r="AL13" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AM13" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AN13" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AO13" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AP13" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AR13" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AS13" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AT13" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>test</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -2650,65 +1935,10 @@
       <c r="AE14" s="1">
         <v>0</v>
       </c>
-      <c r="AF14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="1">
-        <f t="shared" ref="AK14:AT14" si="14">AJ14</f>
-        <v>0</v>
-      </c>
-      <c r="AL14" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AM14" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AN14" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AO14" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AP14" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AR14" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AS14" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AT14" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="15" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>test</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -2801,65 +2031,10 @@
       <c r="AE15" s="1">
         <v>0</v>
       </c>
-      <c r="AF15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="1">
-        <f t="shared" ref="AK15:AT15" si="15">AJ15</f>
-        <v>0</v>
-      </c>
-      <c r="AL15" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AM15" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AN15" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AO15" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AP15" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AR15" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AS15" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AT15" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="16" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>test</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -2952,65 +2127,10 @@
       <c r="AE16" s="1">
         <v>0</v>
       </c>
-      <c r="AF16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="1">
-        <f t="shared" ref="AK16:AT16" si="16">AJ16</f>
-        <v>0</v>
-      </c>
-      <c r="AL16" s="1">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AM16" s="1">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AN16" s="1">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AO16" s="1">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AP16" s="1">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="1">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AR16" s="1">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AS16" s="1">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AT16" s="1">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="17" spans="1:46" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>test</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -3103,64 +2223,9 @@
       <c r="AE17" s="1">
         <v>0</v>
       </c>
-      <c r="AF17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="1">
-        <f t="shared" ref="AK17:AT17" si="17">AJ17</f>
-        <v>0</v>
-      </c>
-      <c r="AL17" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AM17" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AN17" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AO17" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AP17" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AR17" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AS17" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AT17" s="1">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:AT17">
+  <conditionalFormatting sqref="F2:AE17">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
